--- a/test_input.xlsx
+++ b/test_input.xlsx
@@ -413,26 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>MVa</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MIa</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AVa</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AIa</t>
         </is>
@@ -440,170 +445,2892 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75.05298807065321</v>
+        <v>0.004166666666666667</v>
       </c>
       <c r="B2" t="n">
-        <v>35.71354796920848</v>
+        <v>111.4192625274898</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6247251490022614</v>
+        <v>45.62259449817584</v>
       </c>
       <c r="D2" t="n">
-        <v>0.123347571079977</v>
+        <v>-2.38236428228172</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.7440449291314712</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71.77874913575069</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="B3" t="n">
-        <v>35.1106603213991</v>
+        <v>106.8525353357268</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5699063101073389</v>
+        <v>44.29010428255976</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05286120740150011</v>
+        <v>-7.917952258273313</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-2.48390279681916</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68.49271770006891</v>
+        <v>0.0375</v>
       </c>
       <c r="B4" t="n">
-        <v>34.77977973462485</v>
+        <v>98.2662506814051</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4969971043834741</v>
+        <v>41.78408638209315</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03395849591924149</v>
+        <v>-13.37555649981664</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-4.099752960321321</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66.15391498762169</v>
+        <v>0.05416666666666667</v>
       </c>
       <c r="B5" t="n">
-        <v>34.83647250888146</v>
+        <v>86.52173903374111</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4255158727027794</v>
+        <v>38.42594198221961</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1121985427591832</v>
+        <v>-18.59348359272878</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-5.453061880563441</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>65.19069043304005</v>
+        <v>0.07083333333333333</v>
       </c>
       <c r="B6" t="n">
-        <v>35.11817479166136</v>
+        <v>72.7546992025886</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3789219687063859</v>
+        <v>34.64724213316934</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1594201177684528</v>
+        <v>-23.17319191764395</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-6.334632839830103</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>65.58132453941845</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="B7" t="n">
-        <v>35.38240967610316</v>
+        <v>58.26360788487599</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3735906358550438</v>
+        <v>30.93963638911624</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1633925755189807</v>
+        <v>-26.19393664611144</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-6.453832311375056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67.18045346459584</v>
+        <v>0.1041666666666667</v>
       </c>
       <c r="B8" t="n">
-        <v>35.54113618304137</v>
+        <v>44.53742165287529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4105738923542827</v>
+        <v>27.80209358319817</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1239490118424266</v>
+        <v>-25.60272377644336</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-5.496249370117636</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69.79868635880504</v>
+        <v>0.1208333333333333</v>
       </c>
       <c r="B9" t="n">
-        <v>35.69729786088011</v>
+        <v>33.71776853772696</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4759765996700589</v>
+        <v>25.68551606170746</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05199171371621768</v>
+        <v>-17.40725550505549</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-3.32213352467166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72.97561536371394</v>
+        <v>0.1375</v>
       </c>
       <c r="B10" t="n">
-        <v>35.9703378140109</v>
+        <v>29.39164877881107</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5485659533438363</v>
+        <v>24.92247970562447</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03283411543650335</v>
+        <v>1.016374889236626</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.2598025011269928</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>75.86249810904751</v>
+        <v>0.1541666666666667</v>
       </c>
       <c r="B11" t="n">
-        <v>36.30338178473767</v>
+        <v>34.05683529353739</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6090964684014679</v>
+        <v>25.64299745840247</v>
       </c>
       <c r="D11" t="n">
-        <v>0.107646972119832</v>
+        <v>19.10466928312111</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.856058705118007</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>77.48388135304486</v>
+        <v>0.1708333333333333</v>
       </c>
       <c r="B12" t="n">
-        <v>36.46647051923426</v>
+        <v>45.03969747815423</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6451971565558405</v>
+        <v>27.72863063943128</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1534781424986287</v>
+        <v>26.86610910773729</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.164221044562994</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>77.20116896510361</v>
+        <v>0.1875</v>
       </c>
       <c r="B13" t="n">
-        <v>36.25923358636035</v>
+        <v>58.81099371247909</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6508947489754083</v>
+        <v>30.851608176901</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1594071596723056</v>
+        <v>27.21850309898421</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.284063793812488</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.2041666666666667</v>
+      </c>
+      <c r="B14" t="n">
+        <v>73.28232169012909</v>
+      </c>
+      <c r="C14" t="n">
+        <v>34.5594504749594</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24.07923844058874</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6.316004640421626</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.2208333333333334</v>
+      </c>
+      <c r="B15" t="n">
+        <v>86.98394884250004</v>
+      </c>
+      <c r="C15" t="n">
+        <v>38.34917028682847</v>
+      </c>
+      <c r="D15" t="n">
+        <v>19.43882331402557</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.556851560361135</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98.62604031781476</v>
+      </c>
+      <c r="C16" t="n">
+        <v>41.72530035748766</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14.18881499075475</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.293075246960527</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="B17" t="n">
+        <v>107.0809570042899</v>
+      </c>
+      <c r="C17" t="n">
+        <v>44.25342365728192</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8.714578979924321</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.735019122679873</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="B18" t="n">
+        <v>111.4975725780568</v>
+      </c>
+      <c r="C18" t="n">
+        <v>45.6101494226764</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.17184613327922</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.023370765992643</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="B19" t="n">
+        <v>111.4192625274898</v>
+      </c>
+      <c r="C19" t="n">
+        <v>45.62259449817584</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.382364282282225</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.7440449291319874</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0.3041666666666666</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106.8525353357267</v>
+      </c>
+      <c r="C20" t="n">
+        <v>44.29010428255975</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-7.917952258273769</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-2.483902796819648</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0.3208333333333333</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98.26625068140493</v>
+      </c>
+      <c r="C21" t="n">
+        <v>41.78408638209314</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-13.37555649981712</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-4.099752960321833</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="B22" t="n">
+        <v>86.52173903374108</v>
+      </c>
+      <c r="C22" t="n">
+        <v>38.42594198221956</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-18.59348359272968</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-5.453061880563966</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0.3541666666666666</v>
+      </c>
+      <c r="B23" t="n">
+        <v>72.75469920258884</v>
+      </c>
+      <c r="C23" t="n">
+        <v>34.64724213316929</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-23.17319191764526</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-6.334632839830641</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0.3708333333333333</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58.26360788487633</v>
+      </c>
+      <c r="C24" t="n">
+        <v>30.93963638911613</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-26.19393664611296</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-6.453832311375563</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="B25" t="n">
+        <v>44.53742165287559</v>
+      </c>
+      <c r="C25" t="n">
+        <v>27.80209358319806</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-25.60272377644513</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.49624937011804</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0.4041666666666667</v>
+      </c>
+      <c r="B26" t="n">
+        <v>33.71776853772726</v>
+      </c>
+      <c r="C26" t="n">
+        <v>25.68551606170742</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-17.40725550505761</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.322133524671961</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0.4208333333333333</v>
+      </c>
+      <c r="B27" t="n">
+        <v>29.39164877881103</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24.92247970562446</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.016374889234104</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.259802501127313</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="B28" t="n">
+        <v>34.05683529353713</v>
+      </c>
+      <c r="C28" t="n">
+        <v>25.64299745840251</v>
+      </c>
+      <c r="D28" t="n">
+        <v>19.10466928311889</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.856058705117604</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0.4541666666666667</v>
+      </c>
+      <c r="B29" t="n">
+        <v>45.03969747815382</v>
+      </c>
+      <c r="C29" t="n">
+        <v>27.72863063943138</v>
+      </c>
+      <c r="D29" t="n">
+        <v>26.86610910773556</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.164221044562526</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0.4708333333333333</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58.81099371247875</v>
+      </c>
+      <c r="C30" t="n">
+        <v>30.85160817690116</v>
+      </c>
+      <c r="D30" t="n">
+        <v>27.21850309898274</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6.284063793811986</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="B31" t="n">
+        <v>73.28232169012894</v>
+      </c>
+      <c r="C31" t="n">
+        <v>34.5594504749596</v>
+      </c>
+      <c r="D31" t="n">
+        <v>24.07923844058753</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6.316004640421205</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0.5041666666666667</v>
+      </c>
+      <c r="B32" t="n">
+        <v>86.98394884249986</v>
+      </c>
+      <c r="C32" t="n">
+        <v>38.34917028682862</v>
+      </c>
+      <c r="D32" t="n">
+        <v>19.43882331402456</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5.556851560360738</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0.5208333333333333</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98.62604031781461</v>
+      </c>
+      <c r="C33" t="n">
+        <v>41.7253003574878</v>
+      </c>
+      <c r="D33" t="n">
+        <v>14.18881499075367</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.293075246959976</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="B34" t="n">
+        <v>107.0809570042898</v>
+      </c>
+      <c r="C34" t="n">
+        <v>44.25342365728201</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8.714578979923182</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.735019122679189</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="B35" t="n">
+        <v>111.4975725780568</v>
+      </c>
+      <c r="C35" t="n">
+        <v>45.61014942267642</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.171846133278174</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.023370765992035</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0.5708333333333333</v>
+      </c>
+      <c r="B36" t="n">
+        <v>111.4192625274898</v>
+      </c>
+      <c r="C36" t="n">
+        <v>45.62259449817581</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-2.382364282283288</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.744044929132618</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106.8525353357268</v>
+      </c>
+      <c r="C37" t="n">
+        <v>44.29010428255967</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-7.917952258274878</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-2.483902796820304</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98.26625068140503</v>
+      </c>
+      <c r="C38" t="n">
+        <v>41.78408638209301</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-13.37555649981826</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-4.099752960322437</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0.6208333333333333</v>
+      </c>
+      <c r="B39" t="n">
+        <v>86.52173903374117</v>
+      </c>
+      <c r="C39" t="n">
+        <v>38.42594198221943</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-18.5934835927305</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-5.453061880564525</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="B40" t="n">
+        <v>72.75469920258868</v>
+      </c>
+      <c r="C40" t="n">
+        <v>34.64724213316907</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-23.17319191764586</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-6.334632839831249</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0.6541666666666667</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58.26360788487641</v>
+      </c>
+      <c r="C41" t="n">
+        <v>30.93963638911598</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-26.19393664611341</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-6.453832311376303</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0.6708333333333333</v>
+      </c>
+      <c r="B42" t="n">
+        <v>44.53742165287566</v>
+      </c>
+      <c r="C42" t="n">
+        <v>27.80209358319794</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-25.60272377644474</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-5.49624937011883</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="B43" t="n">
+        <v>33.71776853772655</v>
+      </c>
+      <c r="C43" t="n">
+        <v>25.68551606170735</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-17.40725550505462</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-3.322133524672778</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0.7041666666666666</v>
+      </c>
+      <c r="B44" t="n">
+        <v>29.39164877881103</v>
+      </c>
+      <c r="C44" t="n">
+        <v>24.92247970562444</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.016374889237756</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.2598025011281981</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0.7208333333333333</v>
+      </c>
+      <c r="B45" t="n">
+        <v>34.05683529353775</v>
+      </c>
+      <c r="C45" t="n">
+        <v>25.64299745840248</v>
+      </c>
+      <c r="D45" t="n">
+        <v>19.10466928312174</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.856058705116485</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0.7374999999999999</v>
+      </c>
+      <c r="B46" t="n">
+        <v>45.03969747815479</v>
+      </c>
+      <c r="C46" t="n">
+        <v>27.72863063943137</v>
+      </c>
+      <c r="D46" t="n">
+        <v>26.86610910773744</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5.164221044561468</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0.7541666666666667</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58.81099371247961</v>
+      </c>
+      <c r="C47" t="n">
+        <v>30.85160817690113</v>
+      </c>
+      <c r="D47" t="n">
+        <v>27.21850309898399</v>
+      </c>
+      <c r="E47" t="n">
+        <v>6.284063793811106</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0.7708333333333333</v>
+      </c>
+      <c r="B48" t="n">
+        <v>73.28232169012966</v>
+      </c>
+      <c r="C48" t="n">
+        <v>34.55945047495954</v>
+      </c>
+      <c r="D48" t="n">
+        <v>24.07923844058841</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6.316004640420568</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0.7875</v>
+      </c>
+      <c r="B49" t="n">
+        <v>86.98394884250051</v>
+      </c>
+      <c r="C49" t="n">
+        <v>38.34917028682862</v>
+      </c>
+      <c r="D49" t="n">
+        <v>19.43882331402518</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5.556851560360297</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0.8041666666666667</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98.62604031781507</v>
+      </c>
+      <c r="C50" t="n">
+        <v>41.72530035748782</v>
+      </c>
+      <c r="D50" t="n">
+        <v>14.18881499075412</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4.293075246959637</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0.8208333333333333</v>
+      </c>
+      <c r="B51" t="n">
+        <v>107.08095700429</v>
+      </c>
+      <c r="C51" t="n">
+        <v>44.25342365728199</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8.714578979923724</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.735019122679114</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0.8375</v>
+      </c>
+      <c r="B52" t="n">
+        <v>111.4975725780569</v>
+      </c>
+      <c r="C52" t="n">
+        <v>45.61014942267641</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3.171846133278654</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.023370765991984</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="B53" t="n">
+        <v>111.4192625274898</v>
+      </c>
+      <c r="C53" t="n">
+        <v>45.62259449817584</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-2.382364282282636</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.7440449291324919</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0.8708333333333333</v>
+      </c>
+      <c r="B54" t="n">
+        <v>106.8525353357265</v>
+      </c>
+      <c r="C54" t="n">
+        <v>44.29010428255964</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-7.917952258274379</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-2.483902796820419</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98.2662506814047</v>
+      </c>
+      <c r="C55" t="n">
+        <v>41.78408638209304</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-13.3755564998177</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-4.099752960322688</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0.9041666666666667</v>
+      </c>
+      <c r="B56" t="n">
+        <v>86.52173903374054</v>
+      </c>
+      <c r="C56" t="n">
+        <v>38.42594198221945</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-18.5934835927297</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-5.453061880564807</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>0.9208333333333333</v>
+      </c>
+      <c r="B57" t="n">
+        <v>72.75469920258791</v>
+      </c>
+      <c r="C57" t="n">
+        <v>34.64724213316915</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-23.17319191764482</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-6.334632839831688</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58.26360788487533</v>
+      </c>
+      <c r="C58" t="n">
+        <v>30.93963638911613</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-26.19393664611217</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-6.453832311376904</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0.9541666666666666</v>
+      </c>
+      <c r="B59" t="n">
+        <v>44.53742165287457</v>
+      </c>
+      <c r="C59" t="n">
+        <v>27.80209358319803</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-25.6027237764437</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-5.496249370119568</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>0.9708333333333333</v>
+      </c>
+      <c r="B60" t="n">
+        <v>33.71776853772654</v>
+      </c>
+      <c r="C60" t="n">
+        <v>25.68551606170739</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-17.40725550505515</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-3.322133524673757</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>0.9874999999999999</v>
+      </c>
+      <c r="B61" t="n">
+        <v>29.39164877881109</v>
+      </c>
+      <c r="C61" t="n">
+        <v>24.9224797056245</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1.016374889237275</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.2598025011292167</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1.004166666666667</v>
+      </c>
+      <c r="B62" t="n">
+        <v>34.05683529353788</v>
+      </c>
+      <c r="C62" t="n">
+        <v>25.64299745840253</v>
+      </c>
+      <c r="D62" t="n">
+        <v>19.10466928312152</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.85605870511602</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1.020833333333333</v>
+      </c>
+      <c r="B63" t="n">
+        <v>45.03969747815494</v>
+      </c>
+      <c r="C63" t="n">
+        <v>27.72863063943141</v>
+      </c>
+      <c r="D63" t="n">
+        <v>26.86610910773711</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5.164221044561158</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1.0375</v>
+      </c>
+      <c r="B64" t="n">
+        <v>58.81099371247965</v>
+      </c>
+      <c r="C64" t="n">
+        <v>30.85160817690117</v>
+      </c>
+      <c r="D64" t="n">
+        <v>27.21850309898357</v>
+      </c>
+      <c r="E64" t="n">
+        <v>6.284063793810668</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1.054166666666667</v>
+      </c>
+      <c r="B65" t="n">
+        <v>73.28232169012996</v>
+      </c>
+      <c r="C65" t="n">
+        <v>34.55945047495964</v>
+      </c>
+      <c r="D65" t="n">
+        <v>24.07923844058826</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6.316004640420479</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1.070833333333333</v>
+      </c>
+      <c r="B66" t="n">
+        <v>86.98394884250052</v>
+      </c>
+      <c r="C66" t="n">
+        <v>38.34917028682869</v>
+      </c>
+      <c r="D66" t="n">
+        <v>19.43882331402442</v>
+      </c>
+      <c r="E66" t="n">
+        <v>5.556851560359533</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1.0875</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98.62604031781524</v>
+      </c>
+      <c r="C67" t="n">
+        <v>41.72530035748786</v>
+      </c>
+      <c r="D67" t="n">
+        <v>14.18881499075362</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4.293075246959146</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1.104166666666667</v>
+      </c>
+      <c r="B68" t="n">
+        <v>107.0809570042902</v>
+      </c>
+      <c r="C68" t="n">
+        <v>44.25342365728205</v>
+      </c>
+      <c r="D68" t="n">
+        <v>8.714578979923132</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.735019122678589</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1.120833333333333</v>
+      </c>
+      <c r="B69" t="n">
+        <v>111.4975725780569</v>
+      </c>
+      <c r="C69" t="n">
+        <v>45.61014942267638</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3.171846133278062</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.023370765991445</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1.1375</v>
+      </c>
+      <c r="B70" t="n">
+        <v>111.4192625274897</v>
+      </c>
+      <c r="C70" t="n">
+        <v>45.6225944981758</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-2.382364282283406</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.7440449291332153</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1.154166666666667</v>
+      </c>
+      <c r="B71" t="n">
+        <v>106.8525353357265</v>
+      </c>
+      <c r="C71" t="n">
+        <v>44.29010428255962</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-7.917952258274976</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-2.483902796820965</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1.170833333333333</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98.26625068140444</v>
+      </c>
+      <c r="C72" t="n">
+        <v>41.78408638209294</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-13.37555649981827</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-4.099752960323218</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="B73" t="n">
+        <v>86.52173903374042</v>
+      </c>
+      <c r="C73" t="n">
+        <v>38.42594198221936</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-18.5934835927303</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-5.453061880565393</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1.204166666666667</v>
+      </c>
+      <c r="B74" t="n">
+        <v>72.75469920258777</v>
+      </c>
+      <c r="C74" t="n">
+        <v>34.64724213316911</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-23.17319191764555</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-6.334632839832415</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1.220833333333333</v>
+      </c>
+      <c r="B75" t="n">
+        <v>58.26360788487519</v>
+      </c>
+      <c r="C75" t="n">
+        <v>30.93963638911602</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-26.19393664611289</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-6.453832311377592</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1.2375</v>
+      </c>
+      <c r="B76" t="n">
+        <v>44.53742165287449</v>
+      </c>
+      <c r="C76" t="n">
+        <v>27.80209358319799</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-25.6027237764444</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-5.496249370120292</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1.254166666666667</v>
+      </c>
+      <c r="B77" t="n">
+        <v>33.71776853772651</v>
+      </c>
+      <c r="C77" t="n">
+        <v>25.68551606170739</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-17.40725550505604</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-3.322133524674567</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1.270833333333333</v>
+      </c>
+      <c r="B78" t="n">
+        <v>29.39164877881111</v>
+      </c>
+      <c r="C78" t="n">
+        <v>24.92247970562448</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1.01637488923654</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-0.2598025011299957</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1.2875</v>
+      </c>
+      <c r="B79" t="n">
+        <v>34.0568352935379</v>
+      </c>
+      <c r="C79" t="n">
+        <v>25.64299745840248</v>
+      </c>
+      <c r="D79" t="n">
+        <v>19.10466928311992</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.856058705115493</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1.304166666666667</v>
+      </c>
+      <c r="B80" t="n">
+        <v>45.03969747815508</v>
+      </c>
+      <c r="C80" t="n">
+        <v>27.72863063943131</v>
+      </c>
+      <c r="D80" t="n">
+        <v>26.86610910773563</v>
+      </c>
+      <c r="E80" t="n">
+        <v>5.1642210445605</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1.320833333333333</v>
+      </c>
+      <c r="B81" t="n">
+        <v>58.81099371248019</v>
+      </c>
+      <c r="C81" t="n">
+        <v>30.85160817690108</v>
+      </c>
+      <c r="D81" t="n">
+        <v>27.21850309898256</v>
+      </c>
+      <c r="E81" t="n">
+        <v>6.28406379381026</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1.3375</v>
+      </c>
+      <c r="B82" t="n">
+        <v>73.28232169013033</v>
+      </c>
+      <c r="C82" t="n">
+        <v>34.55945047495947</v>
+      </c>
+      <c r="D82" t="n">
+        <v>24.07923844058693</v>
+      </c>
+      <c r="E82" t="n">
+        <v>6.31600464041939</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1.354166666666667</v>
+      </c>
+      <c r="B83" t="n">
+        <v>86.98394884250106</v>
+      </c>
+      <c r="C83" t="n">
+        <v>38.34917028682856</v>
+      </c>
+      <c r="D83" t="n">
+        <v>19.43882331402388</v>
+      </c>
+      <c r="E83" t="n">
+        <v>5.556851560359017</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1.370833333333333</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98.62604031781569</v>
+      </c>
+      <c r="C84" t="n">
+        <v>41.72530035748773</v>
+      </c>
+      <c r="D84" t="n">
+        <v>14.18881499075326</v>
+      </c>
+      <c r="E84" t="n">
+        <v>4.293075246958622</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1.3875</v>
+      </c>
+      <c r="B85" t="n">
+        <v>107.0809570042905</v>
+      </c>
+      <c r="C85" t="n">
+        <v>44.25342365728198</v>
+      </c>
+      <c r="D85" t="n">
+        <v>8.714578979922802</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2.735019122677948</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1.404166666666667</v>
+      </c>
+      <c r="B86" t="n">
+        <v>111.497572578057</v>
+      </c>
+      <c r="C86" t="n">
+        <v>45.61014942267639</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3.171846133277672</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.023370765990646</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1.420833333333333</v>
+      </c>
+      <c r="B87" t="n">
+        <v>111.4192625274896</v>
+      </c>
+      <c r="C87" t="n">
+        <v>45.62259449817583</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-2.382364282283634</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-0.7440449291338284</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="B88" t="n">
+        <v>106.852535335726</v>
+      </c>
+      <c r="C88" t="n">
+        <v>44.29010428255967</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-7.917952258275238</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-2.483902796821519</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1.454166666666667</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98.26625068140406</v>
+      </c>
+      <c r="C89" t="n">
+        <v>41.78408638209308</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-13.3755564998186</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-4.099752960323732</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1.470833333333333</v>
+      </c>
+      <c r="B90" t="n">
+        <v>86.52173903373979</v>
+      </c>
+      <c r="C90" t="n">
+        <v>38.42594198221948</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-18.59348359273091</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-5.453061880565987</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1.4875</v>
+      </c>
+      <c r="B91" t="n">
+        <v>72.75469920258725</v>
+      </c>
+      <c r="C91" t="n">
+        <v>34.64724213316922</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-23.17319191764621</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-6.33463283983281</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1.504166666666667</v>
+      </c>
+      <c r="B92" t="n">
+        <v>58.26360788487482</v>
+      </c>
+      <c r="C92" t="n">
+        <v>30.93963638911615</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-26.19393664611377</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-6.453832311377925</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1.520833333333333</v>
+      </c>
+      <c r="B93" t="n">
+        <v>44.53742165287437</v>
+      </c>
+      <c r="C93" t="n">
+        <v>27.80209358319813</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-25.6027237764454</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-5.496249370120512</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1.5375</v>
+      </c>
+      <c r="B94" t="n">
+        <v>33.71776853772645</v>
+      </c>
+      <c r="C94" t="n">
+        <v>25.68551606170747</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-17.40725550505709</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-3.322133524674678</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1.554166666666667</v>
+      </c>
+      <c r="B95" t="n">
+        <v>29.39164877881109</v>
+      </c>
+      <c r="C95" t="n">
+        <v>24.92247970562448</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1.016374889235224</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-0.2598025011301373</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1.570833333333333</v>
+      </c>
+      <c r="B96" t="n">
+        <v>34.05683529353798</v>
+      </c>
+      <c r="C96" t="n">
+        <v>25.64299745840248</v>
+      </c>
+      <c r="D96" t="n">
+        <v>19.10466928311952</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2.856058705115065</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1.5875</v>
+      </c>
+      <c r="B97" t="n">
+        <v>45.03969747815523</v>
+      </c>
+      <c r="C97" t="n">
+        <v>27.72863063943135</v>
+      </c>
+      <c r="D97" t="n">
+        <v>26.86610910773524</v>
+      </c>
+      <c r="E97" t="n">
+        <v>5.164221044560126</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1.604166666666667</v>
+      </c>
+      <c r="B98" t="n">
+        <v>58.81099371248023</v>
+      </c>
+      <c r="C98" t="n">
+        <v>30.85160817690112</v>
+      </c>
+      <c r="D98" t="n">
+        <v>27.21850309898197</v>
+      </c>
+      <c r="E98" t="n">
+        <v>6.284063793809653</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1.620833333333333</v>
+      </c>
+      <c r="B99" t="n">
+        <v>73.28232169013053</v>
+      </c>
+      <c r="C99" t="n">
+        <v>34.55945047495955</v>
+      </c>
+      <c r="D99" t="n">
+        <v>24.0792384405865</v>
+      </c>
+      <c r="E99" t="n">
+        <v>6.316004640418981</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1.6375</v>
+      </c>
+      <c r="B100" t="n">
+        <v>86.98394884250122</v>
+      </c>
+      <c r="C100" t="n">
+        <v>38.34917028682863</v>
+      </c>
+      <c r="D100" t="n">
+        <v>19.43882331402353</v>
+      </c>
+      <c r="E100" t="n">
+        <v>5.556851560358694</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1.654166666666667</v>
+      </c>
+      <c r="B101" t="n">
+        <v>98.62604031781588</v>
+      </c>
+      <c r="C101" t="n">
+        <v>41.72530035748785</v>
+      </c>
+      <c r="D101" t="n">
+        <v>14.18881499075275</v>
+      </c>
+      <c r="E101" t="n">
+        <v>4.293075246958138</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1.670833333333333</v>
+      </c>
+      <c r="B102" t="n">
+        <v>107.0809570042906</v>
+      </c>
+      <c r="C102" t="n">
+        <v>44.25342365728199</v>
+      </c>
+      <c r="D102" t="n">
+        <v>8.714578979922397</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2.735019122677542</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="B103" t="n">
+        <v>111.4975725780571</v>
+      </c>
+      <c r="C103" t="n">
+        <v>45.61014942267643</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3.171846133277362</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.023370765990355</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1.704166666666667</v>
+      </c>
+      <c r="B104" t="n">
+        <v>111.4192625274896</v>
+      </c>
+      <c r="C104" t="n">
+        <v>45.62259449817581</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-2.382364282284161</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-0.7440449291343366</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1.720833333333333</v>
+      </c>
+      <c r="B105" t="n">
+        <v>106.852535335726</v>
+      </c>
+      <c r="C105" t="n">
+        <v>44.29010428255965</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-7.917952258275616</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-2.483902796821878</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1.7375</v>
+      </c>
+      <c r="B106" t="n">
+        <v>98.26625068140406</v>
+      </c>
+      <c r="C106" t="n">
+        <v>41.78408638209303</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-13.37555649981914</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-4.099752960324263</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1.754166666666667</v>
+      </c>
+      <c r="B107" t="n">
+        <v>86.52173903373959</v>
+      </c>
+      <c r="C107" t="n">
+        <v>38.42594198221942</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-18.59348359273135</v>
+      </c>
+      <c r="E107" t="n">
+        <v>-5.45306188056636</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1.770833333333333</v>
+      </c>
+      <c r="B108" t="n">
+        <v>72.75469920258709</v>
+      </c>
+      <c r="C108" t="n">
+        <v>34.64724213316916</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-23.1731919176467</v>
+      </c>
+      <c r="E108" t="n">
+        <v>-6.334632839833257</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1.7875</v>
+      </c>
+      <c r="B109" t="n">
+        <v>58.26360788487471</v>
+      </c>
+      <c r="C109" t="n">
+        <v>30.9396363891161</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-26.19393664611426</v>
+      </c>
+      <c r="E109" t="n">
+        <v>-6.453832311378375</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1.804166666666667</v>
+      </c>
+      <c r="B110" t="n">
+        <v>44.53742165287414</v>
+      </c>
+      <c r="C110" t="n">
+        <v>27.80209358319804</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-25.60272377644605</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-5.496249370121117</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1.820833333333333</v>
+      </c>
+      <c r="B111" t="n">
+        <v>33.71776853772633</v>
+      </c>
+      <c r="C111" t="n">
+        <v>25.68551606170739</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-17.4072555050575</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-3.322133524675113</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1.8375</v>
+      </c>
+      <c r="B112" t="n">
+        <v>29.39164877881113</v>
+      </c>
+      <c r="C112" t="n">
+        <v>24.9224797056245</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1.016374889234625</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-0.2598025011306689</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1.854166666666667</v>
+      </c>
+      <c r="B113" t="n">
+        <v>34.05683529353797</v>
+      </c>
+      <c r="C113" t="n">
+        <v>25.6429974584025</v>
+      </c>
+      <c r="D113" t="n">
+        <v>19.10466928311893</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2.856058705114499</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1.870833333333333</v>
+      </c>
+      <c r="B114" t="n">
+        <v>45.03969747815519</v>
+      </c>
+      <c r="C114" t="n">
+        <v>27.72863063943138</v>
+      </c>
+      <c r="D114" t="n">
+        <v>26.86610910773455</v>
+      </c>
+      <c r="E114" t="n">
+        <v>5.164221044559421</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1.8875</v>
+      </c>
+      <c r="B115" t="n">
+        <v>58.8109937124803</v>
+      </c>
+      <c r="C115" t="n">
+        <v>30.85160817690117</v>
+      </c>
+      <c r="D115" t="n">
+        <v>27.21850309898136</v>
+      </c>
+      <c r="E115" t="n">
+        <v>6.284063793809084</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1.904166666666667</v>
+      </c>
+      <c r="B116" t="n">
+        <v>73.28232169013066</v>
+      </c>
+      <c r="C116" t="n">
+        <v>34.55945047495964</v>
+      </c>
+      <c r="D116" t="n">
+        <v>24.07923844058615</v>
+      </c>
+      <c r="E116" t="n">
+        <v>6.316004640418685</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1.920833333333333</v>
+      </c>
+      <c r="B117" t="n">
+        <v>86.98394884250128</v>
+      </c>
+      <c r="C117" t="n">
+        <v>38.34917028682867</v>
+      </c>
+      <c r="D117" t="n">
+        <v>19.43882331402285</v>
+      </c>
+      <c r="E117" t="n">
+        <v>5.556851560358052</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="B118" t="n">
+        <v>98.62604031781615</v>
+      </c>
+      <c r="C118" t="n">
+        <v>41.72530035748792</v>
+      </c>
+      <c r="D118" t="n">
+        <v>14.18881499075229</v>
+      </c>
+      <c r="E118" t="n">
+        <v>4.293075246957759</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1.954166666666667</v>
+      </c>
+      <c r="B119" t="n">
+        <v>107.0809570042905</v>
+      </c>
+      <c r="C119" t="n">
+        <v>44.25342365728201</v>
+      </c>
+      <c r="D119" t="n">
+        <v>8.714578979921788</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2.735019122676979</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1.970833333333333</v>
+      </c>
+      <c r="B120" t="n">
+        <v>111.4975725780572</v>
+      </c>
+      <c r="C120" t="n">
+        <v>45.6101494226765</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3.171846133276882</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1.023370765989964</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1.9875</v>
+      </c>
+      <c r="B121" t="n">
+        <v>111.4192625274895</v>
+      </c>
+      <c r="C121" t="n">
+        <v>45.62259449817581</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-2.382364282284493</v>
+      </c>
+      <c r="E121" t="n">
+        <v>-0.7440449291345691</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2.004166666666667</v>
+      </c>
+      <c r="B122" t="n">
+        <v>106.8525353357258</v>
+      </c>
+      <c r="C122" t="n">
+        <v>44.29010428255956</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-7.917952258275638</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-2.483902796821863</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2.020833333333333</v>
+      </c>
+      <c r="B123" t="n">
+        <v>98.26625068140387</v>
+      </c>
+      <c r="C123" t="n">
+        <v>41.784086382093</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-13.37555649981918</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-4.099752960324233</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2.0375</v>
+      </c>
+      <c r="B124" t="n">
+        <v>86.52173903373955</v>
+      </c>
+      <c r="C124" t="n">
+        <v>38.42594198221936</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-18.59348359273168</v>
+      </c>
+      <c r="E124" t="n">
+        <v>-5.453061880566666</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2.054166666666667</v>
+      </c>
+      <c r="B125" t="n">
+        <v>72.75469920258685</v>
+      </c>
+      <c r="C125" t="n">
+        <v>34.64724213316909</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-23.17319191764689</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-6.334632839833383</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2.070833333333333</v>
+      </c>
+      <c r="B126" t="n">
+        <v>58.26360788487455</v>
+      </c>
+      <c r="C126" t="n">
+        <v>30.93963638911603</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-26.19393664611442</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-6.453832311378489</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2.0875</v>
+      </c>
+      <c r="B127" t="n">
+        <v>44.53742165287408</v>
+      </c>
+      <c r="C127" t="n">
+        <v>27.80209358319795</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-25.60272377644647</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-5.496249370121505</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2.104166666666667</v>
+      </c>
+      <c r="B128" t="n">
+        <v>33.71776853772637</v>
+      </c>
+      <c r="C128" t="n">
+        <v>25.68551606170741</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-17.40725550505755</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-3.322133524675298</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2.120833333333334</v>
+      </c>
+      <c r="B129" t="n">
+        <v>29.39164877881102</v>
+      </c>
+      <c r="C129" t="n">
+        <v>24.92247970562447</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.016374889234902</v>
+      </c>
+      <c r="E129" t="n">
+        <v>-0.259802501130557</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2.1375</v>
+      </c>
+      <c r="B130" t="n">
+        <v>34.05683529353806</v>
+      </c>
+      <c r="C130" t="n">
+        <v>25.64299745840256</v>
+      </c>
+      <c r="D130" t="n">
+        <v>19.1046692831179</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2.856058705113434</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2.154166666666667</v>
+      </c>
+      <c r="B131" t="n">
+        <v>45.03969747815526</v>
+      </c>
+      <c r="C131" t="n">
+        <v>27.72863063943143</v>
+      </c>
+      <c r="D131" t="n">
+        <v>26.86610910773346</v>
+      </c>
+      <c r="E131" t="n">
+        <v>5.164221044558375</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2.170833333333333</v>
+      </c>
+      <c r="B132" t="n">
+        <v>58.81099371248034</v>
+      </c>
+      <c r="C132" t="n">
+        <v>30.85160817690121</v>
+      </c>
+      <c r="D132" t="n">
+        <v>27.2185030989806</v>
+      </c>
+      <c r="E132" t="n">
+        <v>6.284063793808324</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2.1875</v>
+      </c>
+      <c r="B133" t="n">
+        <v>73.28232169013084</v>
+      </c>
+      <c r="C133" t="n">
+        <v>34.55945047495969</v>
+      </c>
+      <c r="D133" t="n">
+        <v>24.07923844058524</v>
+      </c>
+      <c r="E133" t="n">
+        <v>6.316004640417784</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2.204166666666667</v>
+      </c>
+      <c r="B134" t="n">
+        <v>86.98394884250155</v>
+      </c>
+      <c r="C134" t="n">
+        <v>38.34917028682873</v>
+      </c>
+      <c r="D134" t="n">
+        <v>19.43882331402224</v>
+      </c>
+      <c r="E134" t="n">
+        <v>5.55685156035749</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2.220833333333334</v>
+      </c>
+      <c r="B135" t="n">
+        <v>98.62604031781621</v>
+      </c>
+      <c r="C135" t="n">
+        <v>41.72530035748796</v>
+      </c>
+      <c r="D135" t="n">
+        <v>14.18881499075146</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4.293075246956933</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2.2375</v>
+      </c>
+      <c r="B136" t="n">
+        <v>107.0809570042907</v>
+      </c>
+      <c r="C136" t="n">
+        <v>44.25342365728208</v>
+      </c>
+      <c r="D136" t="n">
+        <v>8.714578979920992</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2.735019122676232</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2.254166666666667</v>
+      </c>
+      <c r="B137" t="n">
+        <v>111.4975725780572</v>
+      </c>
+      <c r="C137" t="n">
+        <v>45.61014942267646</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.171846133276096</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.023370765989193</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2.270833333333333</v>
+      </c>
+      <c r="B138" t="n">
+        <v>111.4192625274895</v>
+      </c>
+      <c r="C138" t="n">
+        <v>45.6225944981758</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-2.382364282285343</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.7440449291354202</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2.2875</v>
+      </c>
+      <c r="B139" t="n">
+        <v>106.8525353357258</v>
+      </c>
+      <c r="C139" t="n">
+        <v>44.29010428255957</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-7.917952258276851</v>
+      </c>
+      <c r="E139" t="n">
+        <v>-2.483902796823009</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2.304166666666667</v>
+      </c>
+      <c r="B140" t="n">
+        <v>98.2662506814036</v>
+      </c>
+      <c r="C140" t="n">
+        <v>41.78408638209289</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-13.37555649982032</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-4.099752960325316</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2.320833333333333</v>
+      </c>
+      <c r="B141" t="n">
+        <v>86.52173903373942</v>
+      </c>
+      <c r="C141" t="n">
+        <v>38.42594198221929</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-18.59348359273276</v>
+      </c>
+      <c r="E141" t="n">
+        <v>-5.453061880567718</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2.3375</v>
+      </c>
+      <c r="B142" t="n">
+        <v>72.75469920258678</v>
+      </c>
+      <c r="C142" t="n">
+        <v>34.64724213316899</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-23.17319191764813</v>
+      </c>
+      <c r="E142" t="n">
+        <v>-6.334632839834636</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2.354166666666667</v>
+      </c>
+      <c r="B143" t="n">
+        <v>58.26360788487447</v>
+      </c>
+      <c r="C143" t="n">
+        <v>30.93963638911596</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-26.19393664611576</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-6.453832311379815</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2.370833333333334</v>
+      </c>
+      <c r="B144" t="n">
+        <v>44.53742165287397</v>
+      </c>
+      <c r="C144" t="n">
+        <v>27.80209358319795</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-25.60272377644724</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-5.496249370122296</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2.3875</v>
+      </c>
+      <c r="B145" t="n">
+        <v>33.71776853772622</v>
+      </c>
+      <c r="C145" t="n">
+        <v>25.68551606170738</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-17.40725550505864</v>
+      </c>
+      <c r="E145" t="n">
+        <v>-3.322133524676413</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2.404166666666667</v>
+      </c>
+      <c r="B146" t="n">
+        <v>29.391648778811</v>
+      </c>
+      <c r="C146" t="n">
+        <v>24.92247970562442</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1.016374889233352</v>
+      </c>
+      <c r="E146" t="n">
+        <v>-0.2598025011321873</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2.420833333333333</v>
+      </c>
+      <c r="B147" t="n">
+        <v>34.0568352935381</v>
+      </c>
+      <c r="C147" t="n">
+        <v>25.64299745840259</v>
+      </c>
+      <c r="D147" t="n">
+        <v>19.1046692831173</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2.856058705112817</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2.4375</v>
+      </c>
+      <c r="B148" t="n">
+        <v>45.03969747815552</v>
+      </c>
+      <c r="C148" t="n">
+        <v>27.72863063943151</v>
+      </c>
+      <c r="D148" t="n">
+        <v>26.86610910773303</v>
+      </c>
+      <c r="E148" t="n">
+        <v>5.164221044557983</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2.454166666666667</v>
+      </c>
+      <c r="B149" t="n">
+        <v>58.81099371248065</v>
+      </c>
+      <c r="C149" t="n">
+        <v>30.85160817690133</v>
+      </c>
+      <c r="D149" t="n">
+        <v>27.21850309898</v>
+      </c>
+      <c r="E149" t="n">
+        <v>6.28406379380782</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2.470833333333334</v>
+      </c>
+      <c r="B150" t="n">
+        <v>73.28232169013104</v>
+      </c>
+      <c r="C150" t="n">
+        <v>34.55945047495979</v>
+      </c>
+      <c r="D150" t="n">
+        <v>24.07923844058467</v>
+      </c>
+      <c r="E150" t="n">
+        <v>6.31600464041728</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2.4875</v>
+      </c>
+      <c r="B151" t="n">
+        <v>86.98394884250172</v>
+      </c>
+      <c r="C151" t="n">
+        <v>38.34917028682884</v>
+      </c>
+      <c r="D151" t="n">
+        <v>19.43882331402171</v>
+      </c>
+      <c r="E151" t="n">
+        <v>5.55685156035699</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2.504166666666667</v>
+      </c>
+      <c r="B152" t="n">
+        <v>98.62604031781619</v>
+      </c>
+      <c r="C152" t="n">
+        <v>41.72530035748797</v>
+      </c>
+      <c r="D152" t="n">
+        <v>14.188814990751</v>
+      </c>
+      <c r="E152" t="n">
+        <v>4.293075246956507</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2.520833333333333</v>
+      </c>
+      <c r="B153" t="n">
+        <v>107.0809570042909</v>
+      </c>
+      <c r="C153" t="n">
+        <v>44.25342365728214</v>
+      </c>
+      <c r="D153" t="n">
+        <v>8.714578979920569</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2.735019122675828</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2.5375</v>
+      </c>
+      <c r="B154" t="n">
+        <v>111.4975725780572</v>
+      </c>
+      <c r="C154" t="n">
+        <v>45.61014942267651</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3.17184613327567</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1.023370765988809</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2.554166666666667</v>
+      </c>
+      <c r="B155" t="n">
+        <v>111.4192625274895</v>
+      </c>
+      <c r="C155" t="n">
+        <v>45.62259449817577</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-2.382364282285674</v>
+      </c>
+      <c r="E155" t="n">
+        <v>-0.7440449291356946</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2.570833333333333</v>
+      </c>
+      <c r="B156" t="n">
+        <v>106.8525353357258</v>
+      </c>
+      <c r="C156" t="n">
+        <v>44.29010428255953</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-7.917952258277401</v>
+      </c>
+      <c r="E156" t="n">
+        <v>-2.483902796823557</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2.5875</v>
+      </c>
+      <c r="B157" t="n">
+        <v>98.26625068140335</v>
+      </c>
+      <c r="C157" t="n">
+        <v>41.78408638209282</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-13.37555649982078</v>
+      </c>
+      <c r="E157" t="n">
+        <v>-4.099752960325706</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2.604166666666667</v>
+      </c>
+      <c r="B158" t="n">
+        <v>86.52173903373921</v>
+      </c>
+      <c r="C158" t="n">
+        <v>38.4259419822192</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-18.59348359273336</v>
+      </c>
+      <c r="E158" t="n">
+        <v>-5.453061880568296</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2.620833333333334</v>
+      </c>
+      <c r="B159" t="n">
+        <v>72.75469920258662</v>
+      </c>
+      <c r="C159" t="n">
+        <v>34.64724213316898</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-23.1731919176487</v>
+      </c>
+      <c r="E159" t="n">
+        <v>-6.334632839835135</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2.6375</v>
+      </c>
+      <c r="B160" t="n">
+        <v>58.26360788487432</v>
+      </c>
+      <c r="C160" t="n">
+        <v>30.93963638911591</v>
+      </c>
+      <c r="D160" t="n">
+        <v>-26.19393664611614</v>
+      </c>
+      <c r="E160" t="n">
+        <v>-6.453832311380175</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2.654166666666667</v>
+      </c>
+      <c r="B161" t="n">
+        <v>44.53742165287386</v>
+      </c>
+      <c r="C161" t="n">
+        <v>27.80209358319789</v>
+      </c>
+      <c r="D161" t="n">
+        <v>-25.60272377644784</v>
+      </c>
+      <c r="E161" t="n">
+        <v>-5.49624937012288</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2.670833333333333</v>
+      </c>
+      <c r="B162" t="n">
+        <v>33.71776853772609</v>
+      </c>
+      <c r="C162" t="n">
+        <v>25.68551606170731</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-17.40725550505952</v>
+      </c>
+      <c r="E162" t="n">
+        <v>-3.322133524677156</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2.6875</v>
+      </c>
+      <c r="B163" t="n">
+        <v>29.39164877881107</v>
+      </c>
+      <c r="C163" t="n">
+        <v>24.92247970562447</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1.01637488923271</v>
+      </c>
+      <c r="E163" t="n">
+        <v>-0.2598025011327866</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2.704166666666667</v>
+      </c>
+      <c r="B164" t="n">
+        <v>34.05683529353797</v>
+      </c>
+      <c r="C164" t="n">
+        <v>25.64299745840254</v>
+      </c>
+      <c r="D164" t="n">
+        <v>19.10466928311665</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2.856058705112194</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2.720833333333334</v>
+      </c>
+      <c r="B165" t="n">
+        <v>45.03969747815188</v>
+      </c>
+      <c r="C165" t="n">
+        <v>27.72863063943149</v>
+      </c>
+      <c r="D165" t="n">
+        <v>26.86610910772368</v>
+      </c>
+      <c r="E165" t="n">
+        <v>5.164221044557617</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2.7375</v>
+      </c>
+      <c r="B166" t="n">
+        <v>58.81099371247735</v>
+      </c>
+      <c r="C166" t="n">
+        <v>30.85160817690144</v>
+      </c>
+      <c r="D166" t="n">
+        <v>27.21850309897249</v>
+      </c>
+      <c r="E166" t="n">
+        <v>6.28406379380738</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2.754166666666667</v>
+      </c>
+      <c r="B167" t="n">
+        <v>73.2823216901277</v>
+      </c>
+      <c r="C167" t="n">
+        <v>34.55945047495977</v>
+      </c>
+      <c r="D167" t="n">
+        <v>24.07923844057826</v>
+      </c>
+      <c r="E167" t="n">
+        <v>6.316004640416624</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2.770833333333333</v>
+      </c>
+      <c r="B168" t="n">
+        <v>86.98394884249933</v>
+      </c>
+      <c r="C168" t="n">
+        <v>38.34917028682892</v>
+      </c>
+      <c r="D168" t="n">
+        <v>19.43882331401624</v>
+      </c>
+      <c r="E168" t="n">
+        <v>5.556851560356577</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2.7875</v>
+      </c>
+      <c r="B169" t="n">
+        <v>98.62604031781463</v>
+      </c>
+      <c r="C169" t="n">
+        <v>41.72530035748805</v>
+      </c>
+      <c r="D169" t="n">
+        <v>14.18881499074612</v>
+      </c>
+      <c r="E169" t="n">
+        <v>4.293075246956255</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2.804166666666667</v>
+      </c>
+      <c r="B170" t="n">
+        <v>107.0809570042899</v>
+      </c>
+      <c r="C170" t="n">
+        <v>44.2534236572822</v>
+      </c>
+      <c r="D170" t="n">
+        <v>8.714578979915911</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2.735019122675492</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2.820833333333333</v>
+      </c>
+      <c r="B171" t="n">
+        <v>111.4975725780568</v>
+      </c>
+      <c r="C171" t="n">
+        <v>45.61014942267645</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3.171846133270884</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1.023370765988198</v>
       </c>
     </row>
   </sheetData>
